--- a/stationnary_data.xlsx
+++ b/stationnary_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liessenathan/Desktop/M2/Gestion quantitative/Projet/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liessenathan/Desktop/M2/Gestion quantitative/Projet/Repo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A41BC2E-444A-BB4A-A89E-6373D3DBFC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9026B56B-BC92-1040-A208-8E273B16E1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -114,7 +114,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -478,9 +478,6 @@
       <c r="G3">
         <v>100.0065</v>
       </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
@@ -501,9 +498,6 @@
       <c r="G4">
         <v>100.3623</v>
       </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
@@ -524,9 +518,6 @@
       <c r="G5">
         <v>100.6661</v>
       </c>
-      <c r="I5">
-        <v>-1.005033585350157E-2</v>
-      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
@@ -547,9 +538,6 @@
       <c r="G6">
         <v>100.8976</v>
       </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
@@ -564,17 +552,11 @@
       <c r="D7">
         <v>4.285547070443485E-3</v>
       </c>
-      <c r="E7">
-        <v>4.5570298106601559</v>
-      </c>
       <c r="F7">
         <v>6.6177305513059892E-3</v>
       </c>
       <c r="G7">
         <v>101.03830000000001</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -596,9 +578,6 @@
       <c r="G8">
         <v>101.0847</v>
       </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
@@ -619,9 +598,6 @@
       <c r="G9">
         <v>101.0565</v>
       </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
@@ -642,9 +618,6 @@
       <c r="G10">
         <v>100.9898</v>
       </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
@@ -665,9 +638,6 @@
       <c r="G11">
         <v>100.9235</v>
       </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
@@ -688,9 +658,6 @@
       <c r="G12">
         <v>100.8888</v>
       </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
@@ -705,17 +672,11 @@
       <c r="D13">
         <v>5.1592756882126167E-3</v>
       </c>
-      <c r="E13">
-        <v>4.5411648560121796</v>
-      </c>
       <c r="F13">
         <v>6.669637806361095E-3</v>
       </c>
       <c r="G13">
         <v>100.90300000000001</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -737,9 +698,6 @@
       <c r="G14">
         <v>100.9605</v>
       </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
@@ -760,9 +718,6 @@
       <c r="G15">
         <v>101.02030000000001</v>
       </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
@@ -777,20 +732,14 @@
       <c r="D16">
         <v>4.3939144294942167E-3</v>
       </c>
-      <c r="E16">
-        <v>4.6051701859880918</v>
-      </c>
       <c r="F16">
         <v>9.059577182908285E-4</v>
       </c>
       <c r="G16">
         <v>101.03100000000001</v>
       </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>22006</v>
       </c>
@@ -809,11 +758,8 @@
       <c r="G17">
         <v>100.9543</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>22036</v>
       </c>
@@ -832,11 +778,8 @@
       <c r="G18">
         <v>100.7927</v>
       </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>22067</v>
       </c>
@@ -849,20 +792,14 @@
       <c r="D19">
         <v>-6.1855112669544354E-3</v>
       </c>
-      <c r="E19">
-        <v>4.535820107853298</v>
-      </c>
       <c r="F19">
         <v>2.4270906414418651E-3</v>
       </c>
       <c r="G19">
         <v>100.5655</v>
       </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>22097</v>
       </c>
@@ -881,11 +818,8 @@
       <c r="G20">
         <v>100.29040000000001</v>
       </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>22128</v>
       </c>
@@ -904,11 +838,8 @@
       <c r="G21">
         <v>99.97045</v>
       </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>22159</v>
       </c>
@@ -921,20 +852,14 @@
       <c r="D22">
         <v>-6.2627790365077374E-4</v>
       </c>
-      <c r="E22">
-        <v>4.5767707114663931</v>
-      </c>
       <c r="F22">
         <v>-2.540403531442692E-3</v>
       </c>
       <c r="G22">
         <v>99.605130000000003</v>
       </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>22189</v>
       </c>
@@ -953,11 +878,8 @@
       <c r="G23">
         <v>99.20438</v>
       </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>22220</v>
       </c>
@@ -976,11 +898,8 @@
       <c r="G24">
         <v>98.805430000000001</v>
       </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>22250</v>
       </c>
@@ -993,20 +912,14 @@
       <c r="D25">
         <v>-3.3486613532911491E-3</v>
       </c>
-      <c r="E25">
-        <v>4.5009201646142918</v>
-      </c>
       <c r="F25">
         <v>-5.7495024912608272E-3</v>
       </c>
       <c r="G25">
         <v>98.455629999999999</v>
       </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>22281</v>
       </c>
@@ -1025,11 +938,8 @@
       <c r="G26">
         <v>98.195819999999998</v>
       </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>22312</v>
       </c>
@@ -1048,11 +958,8 @@
       <c r="G27">
         <v>98.040310000000005</v>
       </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>22340</v>
       </c>
@@ -1065,20 +972,14 @@
       <c r="D28">
         <v>-2.3498705330080578E-3</v>
       </c>
-      <c r="E28">
-        <v>4.517431271680084</v>
-      </c>
       <c r="F28">
         <v>7.8225838033851858E-5</v>
       </c>
       <c r="G28">
         <v>97.989980000000003</v>
       </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>22371</v>
       </c>
@@ -1097,11 +998,8 @@
       <c r="G29">
         <v>98.037239999999997</v>
       </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>22401</v>
       </c>
@@ -1120,11 +1018,8 @@
       <c r="G30">
         <v>98.162859999999995</v>
       </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>22432</v>
       </c>
@@ -1137,20 +1032,14 @@
       <c r="D31">
         <v>2.960537665520846E-3</v>
       </c>
-      <c r="E31">
-        <v>4.5272086445183799</v>
-      </c>
       <c r="F31">
         <v>5.9551606775052326E-3</v>
       </c>
       <c r="G31">
         <v>98.346029999999999</v>
       </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>22462</v>
       </c>
@@ -1168,9 +1057,6 @@
       </c>
       <c r="G32">
         <v>98.568259999999995</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
@@ -1192,9 +1078,6 @@
       <c r="G33">
         <v>98.812870000000004</v>
       </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
@@ -1209,17 +1092,11 @@
       <c r="D34">
         <v>3.2281597102610249E-3</v>
       </c>
-      <c r="E34">
-        <v>4.5971380142908274</v>
-      </c>
       <c r="F34">
         <v>4.2645611598235433E-3</v>
       </c>
       <c r="G34">
         <v>99.066299999999998</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
@@ -1241,9 +1118,6 @@
       <c r="G35">
         <v>99.31747</v>
       </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
@@ -1264,9 +1138,6 @@
       <c r="G36">
         <v>99.555959999999999</v>
       </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
@@ -1281,17 +1152,11 @@
       <c r="D37">
         <v>4.0269493575042503E-3</v>
       </c>
-      <c r="E37">
-        <v>4.5325994931532563</v>
-      </c>
       <c r="F37">
         <v>9.1505615246525451E-3</v>
       </c>
       <c r="G37">
         <v>99.771600000000007</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
@@ -1313,9 +1178,6 @@
       <c r="G38">
         <v>99.954419999999999</v>
       </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
@@ -1336,9 +1198,6 @@
       <c r="G39">
         <v>100.0959</v>
       </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
       <c r="J39">
         <v>0.80363636363636359</v>
       </c>
@@ -1356,17 +1215,11 @@
       <c r="D40">
         <v>5.3961376952482709E-3</v>
       </c>
-      <c r="E40">
-        <v>4.604169685654508</v>
-      </c>
       <c r="F40">
         <v>4.8386893305583101E-3</v>
       </c>
       <c r="G40">
         <v>100.1891</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
       </c>
       <c r="J40">
         <v>0.75555555555555554</v>
@@ -1391,9 +1244,6 @@
       <c r="G41">
         <v>100.2317</v>
       </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
       <c r="J41">
         <v>0.8722727272727272</v>
       </c>
@@ -1417,9 +1267,6 @@
       <c r="G42">
         <v>100.2316</v>
       </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
       <c r="J42">
         <v>0.85549999999999993</v>
       </c>
@@ -1437,17 +1284,11 @@
       <c r="D43">
         <v>4.6749978375437712E-4</v>
       </c>
-      <c r="E43">
-        <v>4.558078578454241</v>
-      </c>
       <c r="F43">
         <v>1.417692307458474E-3</v>
       </c>
       <c r="G43">
         <v>100.19889999999999</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
       </c>
       <c r="J43">
         <v>0.84772727272727277</v>
@@ -1472,9 +1313,6 @@
       <c r="G44">
         <v>100.1399</v>
       </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
       <c r="J44">
         <v>0.88095238095238093</v>
       </c>
@@ -1498,9 +1336,6 @@
       <c r="G45">
         <v>100.05419999999999</v>
       </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
       <c r="J45">
         <v>0.72380952380952379</v>
       </c>
@@ -1518,17 +1353,11 @@
       <c r="D46">
         <v>1.648982306546642E-3</v>
       </c>
-      <c r="E46">
-        <v>4.517431271680084</v>
-      </c>
       <c r="F46">
         <v>1.1187500039087079E-3</v>
       </c>
       <c r="G46">
         <v>99.939030000000002</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
       </c>
       <c r="J46">
         <v>0.77652173913043476</v>
@@ -1553,9 +1382,6 @@
       <c r="G47">
         <v>99.796390000000002</v>
       </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
       <c r="J47">
         <v>0.91842105263157914</v>
       </c>
@@ -1579,9 +1405,6 @@
       <c r="G48">
         <v>99.641170000000002</v>
       </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
       <c r="J48">
         <v>0.95045454545454533</v>
       </c>
@@ -1599,17 +1422,11 @@
       <c r="D49">
         <v>2.6762536177571411E-4</v>
       </c>
-      <c r="E49">
-        <v>4.5538768916005408</v>
-      </c>
       <c r="F49">
         <v>4.7642165589074637E-3</v>
       </c>
       <c r="G49">
         <v>99.493080000000006</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
       </c>
       <c r="J49">
         <v>0.91368421052631577</v>
@@ -1634,9 +1451,6 @@
       <c r="G50">
         <v>99.369460000000004</v>
       </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
       <c r="J50">
         <v>0.85850000000000004</v>
       </c>
@@ -1660,9 +1474,6 @@
       <c r="G51">
         <v>99.2774</v>
       </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
       <c r="J51">
         <v>0.79500000000000004</v>
       </c>
@@ -1680,17 +1491,11 @@
       <c r="D52">
         <v>2.0472658358912099E-3</v>
       </c>
-      <c r="E52">
-        <v>4.5890408040582082</v>
-      </c>
       <c r="F52">
         <v>2.6334534792278319E-3</v>
       </c>
       <c r="G52">
         <v>99.219560000000001</v>
-      </c>
-      <c r="I52">
-        <v>0</v>
       </c>
       <c r="J52">
         <v>0.91055555555555556</v>
@@ -1715,9 +1520,6 @@
       <c r="G53">
         <v>99.197360000000003</v>
       </c>
-      <c r="I53">
-        <v>0</v>
-      </c>
       <c r="J53">
         <v>0.89714285714285713</v>
       </c>
@@ -1741,9 +1543,6 @@
       <c r="G54">
         <v>99.211479999999995</v>
       </c>
-      <c r="I54">
-        <v>0</v>
-      </c>
       <c r="J54">
         <v>0.85619047619047639</v>
       </c>
@@ -1761,17 +1560,11 @@
       <c r="D55">
         <v>6.3606490006229421E-4</v>
       </c>
-      <c r="E55">
-        <v>4.5185223792624187</v>
-      </c>
       <c r="F55">
         <v>4.224912104311862E-3</v>
       </c>
       <c r="G55">
         <v>99.260429999999999</v>
-      </c>
-      <c r="I55">
-        <v>0</v>
       </c>
       <c r="J55">
         <v>0.81272727272727285</v>
@@ -1796,9 +1589,6 @@
       <c r="G56">
         <v>99.336209999999994</v>
       </c>
-      <c r="I56">
-        <v>0</v>
-      </c>
       <c r="J56">
         <v>0.79600000000000004</v>
       </c>
@@ -1822,9 +1612,6 @@
       <c r="G57">
         <v>99.417230000000004</v>
       </c>
-      <c r="I57">
-        <v>0</v>
-      </c>
       <c r="J57">
         <v>0.54545454545454541</v>
       </c>
@@ -1842,17 +1629,11 @@
       <c r="D58">
         <v>2.0403862703854969E-3</v>
       </c>
-      <c r="E58">
-        <v>4.5685062016164997</v>
-      </c>
       <c r="F58">
         <v>3.55673713397664E-3</v>
       </c>
       <c r="G58">
         <v>99.481070000000003</v>
-      </c>
-      <c r="I58">
-        <v>0</v>
       </c>
       <c r="J58">
         <v>0.46863636363636368</v>
@@ -1877,9 +1658,6 @@
       <c r="G59">
         <v>99.516540000000006</v>
       </c>
-      <c r="I59">
-        <v>0</v>
-      </c>
       <c r="J59">
         <v>0.50350000000000006</v>
       </c>
@@ -1903,9 +1681,6 @@
       <c r="G60">
         <v>99.536569999999998</v>
       </c>
-      <c r="I60">
-        <v>0</v>
-      </c>
       <c r="J60">
         <v>0.46652173913043482</v>
       </c>
@@ -1923,17 +1698,11 @@
       <c r="D61">
         <v>-4.8892071727735242E-4</v>
       </c>
-      <c r="E61">
-        <v>4.5475410731514554</v>
-      </c>
       <c r="F61">
         <v>2.369221840642588E-3</v>
       </c>
       <c r="G61">
         <v>99.562340000000006</v>
-      </c>
-      <c r="I61">
-        <v>0</v>
       </c>
       <c r="J61">
         <v>0.38117647058823528</v>
@@ -1958,9 +1727,6 @@
       <c r="G62">
         <v>99.608379999999997</v>
       </c>
-      <c r="I62">
-        <v>0</v>
-      </c>
       <c r="J62">
         <v>0.31714285714285723</v>
       </c>
@@ -1984,9 +1750,6 @@
       <c r="G63">
         <v>99.66704</v>
       </c>
-      <c r="I63">
-        <v>0</v>
-      </c>
       <c r="J63">
         <v>0.37454545454545463</v>
       </c>
@@ -2004,17 +1767,11 @@
       <c r="D64">
         <v>4.6164608193244314E-3</v>
       </c>
-      <c r="E64">
-        <v>4.6001576441645469</v>
-      </c>
       <c r="F64">
         <v>8.9507293622599349E-3</v>
       </c>
       <c r="G64">
         <v>99.721019999999996</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
       </c>
       <c r="J64">
         <v>0.36333333333333329</v>
@@ -2039,9 +1796,6 @@
       <c r="G65">
         <v>99.754630000000006</v>
       </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
       <c r="J65">
         <v>0.30666666666666659</v>
       </c>
@@ -2065,9 +1819,6 @@
       <c r="G66">
         <v>99.765079999999998</v>
       </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
       <c r="J66">
         <v>0.32227272727272738</v>
       </c>
@@ -2085,17 +1836,11 @@
       <c r="D67">
         <v>2.8790393213302679E-3</v>
       </c>
-      <c r="E67">
-        <v>4.590056548178044</v>
-      </c>
       <c r="F67">
         <v>6.2885964782690706E-3</v>
       </c>
       <c r="G67">
         <v>99.754999999999995</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
       </c>
       <c r="J67">
         <v>0.36100000000000021</v>
@@ -2120,9 +1865,6 @@
       <c r="G68">
         <v>99.726590000000002</v>
       </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
       <c r="J68">
         <v>0.33681818181818202</v>
       </c>
@@ -2146,9 +1888,6 @@
       <c r="G69">
         <v>99.676990000000004</v>
       </c>
-      <c r="I69">
-        <v>-1.6978336534418052E-2</v>
-      </c>
       <c r="J69">
         <v>0.47090909090909111</v>
       </c>
@@ -2166,17 +1905,11 @@
       <c r="D70">
         <v>3.5375279347906741E-3</v>
       </c>
-      <c r="E70">
-        <v>4.6111522576656396</v>
-      </c>
       <c r="F70">
         <v>6.0611210210392841E-3</v>
       </c>
       <c r="G70">
         <v>99.604820000000004</v>
-      </c>
-      <c r="I70">
-        <v>0</v>
       </c>
       <c r="J70">
         <v>0.45000000000000018</v>
@@ -2201,9 +1934,6 @@
       <c r="G71">
         <v>99.518010000000004</v>
       </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
       <c r="J71">
         <v>0.3633333333333334</v>
       </c>
@@ -2227,9 +1957,6 @@
       <c r="G72">
         <v>99.443060000000003</v>
       </c>
-      <c r="I72">
-        <v>0</v>
-      </c>
       <c r="J72">
         <v>0.32428571428571451</v>
       </c>
@@ -2247,17 +1974,11 @@
       <c r="D73">
         <v>7.2027495301441036E-3</v>
       </c>
-      <c r="E73">
-        <v>4.604169685654508</v>
-      </c>
       <c r="F73">
         <v>7.3516645579339013E-3</v>
       </c>
       <c r="G73">
         <v>99.410129999999995</v>
-      </c>
-      <c r="I73">
-        <v>0</v>
       </c>
       <c r="J73">
         <v>0.24500000000000011</v>
@@ -2282,9 +2003,6 @@
       <c r="G74">
         <v>99.437619999999995</v>
       </c>
-      <c r="I74">
-        <v>0</v>
-      </c>
       <c r="J74">
         <v>0.1577272727272728</v>
       </c>
@@ -2308,9 +2026,6 @@
       <c r="G75">
         <v>99.513570000000001</v>
       </c>
-      <c r="I75">
-        <v>0</v>
-      </c>
       <c r="J75">
         <v>0.24750000000000011</v>
       </c>
@@ -2328,17 +2043,11 @@
       <c r="D76">
         <v>3.652145923339845E-3</v>
       </c>
-      <c r="E76">
-        <v>4.6249728132842707</v>
-      </c>
       <c r="F76">
         <v>5.4405886575104026E-3</v>
       </c>
       <c r="G76">
         <v>99.615549999999999</v>
-      </c>
-      <c r="I76">
-        <v>0</v>
       </c>
       <c r="J76">
         <v>0.18388888888888891</v>
@@ -2363,9 +2072,6 @@
       <c r="G77">
         <v>99.726699999999994</v>
       </c>
-      <c r="I77">
-        <v>0</v>
-      </c>
       <c r="J77">
         <v>0.1469565217391306</v>
       </c>
@@ -2389,9 +2095,6 @@
       <c r="G78">
         <v>99.849609999999998</v>
       </c>
-      <c r="I78">
-        <v>0</v>
-      </c>
       <c r="J78">
         <v>0.16714285714285709</v>
       </c>
@@ -2409,17 +2112,11 @@
       <c r="D79">
         <v>3.8426548318977178E-3</v>
       </c>
-      <c r="E79">
-        <v>4.6577626361072619</v>
-      </c>
       <c r="F79">
         <v>6.3970114665838906E-3</v>
       </c>
       <c r="G79">
         <v>99.997150000000005</v>
-      </c>
-      <c r="I79">
-        <v>0</v>
       </c>
       <c r="J79">
         <v>0.18099999999999999</v>
@@ -2444,9 +2141,6 @@
       <c r="G80">
         <v>100.1824</v>
       </c>
-      <c r="I80">
-        <v>0</v>
-      </c>
       <c r="J80">
         <v>0.22363636363636391</v>
       </c>
@@ -2470,9 +2164,6 @@
       <c r="G81">
         <v>100.40649999999999</v>
       </c>
-      <c r="I81">
-        <v>0</v>
-      </c>
       <c r="J81">
         <v>0.22000000000000011</v>
       </c>
@@ -2490,17 +2181,11 @@
       <c r="D82">
         <v>4.3046722172324081E-3</v>
       </c>
-      <c r="E82">
-        <v>4.6386049620743286</v>
-      </c>
       <c r="F82">
         <v>5.3102934297175608E-3</v>
       </c>
       <c r="G82">
         <v>100.6641</v>
-      </c>
-      <c r="I82">
-        <v>0</v>
       </c>
       <c r="J82">
         <v>0.1836363636363636</v>
@@ -2525,9 +2210,6 @@
       <c r="G83">
         <v>100.9453</v>
       </c>
-      <c r="I83">
-        <v>0</v>
-      </c>
       <c r="J83">
         <v>8.5714285714285535E-2</v>
       </c>
@@ -2551,9 +2233,6 @@
       <c r="G84">
         <v>101.2355</v>
       </c>
-      <c r="I84">
-        <v>0</v>
-      </c>
       <c r="J84">
         <v>5.1499999999999921E-2</v>
       </c>
@@ -2571,17 +2250,11 @@
       <c r="D85">
         <v>4.4780416746004192E-3</v>
       </c>
-      <c r="E85">
-        <v>4.6337576428400036</v>
-      </c>
       <c r="F85">
         <v>7.0245544280815864E-3</v>
       </c>
       <c r="G85">
         <v>101.5158</v>
-      </c>
-      <c r="I85">
-        <v>0</v>
       </c>
       <c r="J85">
         <v>7.4210526315789574E-2</v>
@@ -2606,9 +2279,6 @@
       <c r="G86">
         <v>101.7627</v>
       </c>
-      <c r="I86">
-        <v>0</v>
-      </c>
       <c r="J86">
         <v>-0.10181818181818179</v>
       </c>
@@ -2632,9 +2302,6 @@
       <c r="G87">
         <v>101.949</v>
       </c>
-      <c r="I87">
-        <v>0</v>
-      </c>
       <c r="J87">
         <v>-0.26428571428571418</v>
       </c>
@@ -2652,17 +2319,11 @@
       <c r="D88">
         <v>4.2609280504262159E-3</v>
       </c>
-      <c r="E88">
-        <v>4.6051701859880918</v>
-      </c>
       <c r="F88">
         <v>5.0860422234677571E-3</v>
       </c>
       <c r="G88">
         <v>102.04989999999999</v>
-      </c>
-      <c r="I88">
-        <v>0</v>
       </c>
       <c r="J88">
         <v>-0.11</v>
@@ -2687,9 +2348,6 @@
       <c r="G89">
         <v>102.0544</v>
       </c>
-      <c r="I89">
-        <v>0</v>
-      </c>
       <c r="J89">
         <v>-9.6956521739130372E-2</v>
       </c>
@@ -2713,9 +2371,6 @@
       <c r="G90">
         <v>101.9819</v>
       </c>
-      <c r="I90">
-        <v>0</v>
-      </c>
       <c r="J90">
         <v>-0.14949999999999999</v>
       </c>
@@ -2733,17 +2388,11 @@
       <c r="D91">
         <v>4.3256404501406109E-3</v>
       </c>
-      <c r="E91">
-        <v>4.5612182984589076</v>
-      </c>
       <c r="F91">
         <v>3.418000852526859E-3</v>
       </c>
       <c r="G91">
         <v>101.8635</v>
-      </c>
-      <c r="I91">
-        <v>0</v>
       </c>
       <c r="J91">
         <v>-0.15619047619047641</v>
@@ -2768,9 +2417,6 @@
       <c r="G92">
         <v>101.7282</v>
       </c>
-      <c r="I92">
-        <v>0</v>
-      </c>
       <c r="J92">
         <v>-0.15090909090909099</v>
       </c>
@@ -2794,9 +2440,6 @@
       <c r="G93">
         <v>101.5933</v>
       </c>
-      <c r="I93">
-        <v>0</v>
-      </c>
       <c r="J93">
         <v>-0.1545</v>
       </c>
@@ -2814,17 +2457,11 @@
       <c r="D94">
         <v>3.1985618226926249E-3</v>
       </c>
-      <c r="E94">
-        <v>4.5130548970802851</v>
-      </c>
       <c r="F94">
         <v>2.7621515809688191E-3</v>
       </c>
       <c r="G94">
         <v>101.46680000000001</v>
-      </c>
-      <c r="I94">
-        <v>0</v>
       </c>
       <c r="J94">
         <v>-0.32</v>
@@ -2849,9 +2486,6 @@
       <c r="G95">
         <v>101.3502</v>
       </c>
-      <c r="I95">
-        <v>1.6978336534418052E-2</v>
-      </c>
       <c r="J95">
         <v>-0.63952380952380949</v>
       </c>
@@ -2875,9 +2509,6 @@
       <c r="G96">
         <v>101.2406</v>
       </c>
-      <c r="I96">
-        <v>0</v>
-      </c>
       <c r="J96">
         <v>-0.56799999999999995</v>
       </c>
@@ -2895,17 +2526,11 @@
       <c r="D97">
         <v>2.540945212254897E-3</v>
       </c>
-      <c r="E97">
-        <v>4.4807401076099147</v>
-      </c>
       <c r="F97">
         <v>3.9994874127327051E-3</v>
       </c>
       <c r="G97">
         <v>101.13200000000001</v>
-      </c>
-      <c r="I97">
-        <v>0</v>
       </c>
       <c r="J97">
         <v>-0.38684210526315782</v>
@@ -2930,9 +2555,6 @@
       <c r="G98">
         <v>101.01649999999999</v>
       </c>
-      <c r="I98">
-        <v>0</v>
-      </c>
       <c r="J98">
         <v>-0.36190476190476201</v>
       </c>
@@ -2956,9 +2578,6 @@
       <c r="G99">
         <v>100.8853</v>
       </c>
-      <c r="I99">
-        <v>0</v>
-      </c>
       <c r="J99">
         <v>-0.16714285714285701</v>
       </c>
@@ -2976,9 +2595,6 @@
       <c r="D100">
         <v>3.3629888115349621E-4</v>
       </c>
-      <c r="E100">
-        <v>4.5443580465913342</v>
-      </c>
       <c r="F100">
         <v>-1.7104250447808061E-4</v>
       </c>
@@ -2987,9 +2603,6 @@
       </c>
       <c r="H100">
         <v>5.3050115599972969E-3</v>
-      </c>
-      <c r="I100">
-        <v>1.005033585350157E-2</v>
       </c>
       <c r="J100">
         <v>-8.66666666666666E-2</v>
@@ -3017,9 +2630,6 @@
       <c r="H101">
         <v>5.4234151293499622E-3</v>
       </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
       <c r="J101">
         <v>0.19090909090909089</v>
       </c>
@@ -3046,9 +2656,6 @@
       <c r="H102">
         <v>3.9105871784119728E-3</v>
       </c>
-      <c r="I102">
-        <v>0</v>
-      </c>
       <c r="J102">
         <v>0.48849999999999999</v>
       </c>
@@ -3066,9 +2673,6 @@
       <c r="D103">
         <v>2.3496036319379239E-3</v>
       </c>
-      <c r="E103">
-        <v>4.5633059818893926</v>
-      </c>
       <c r="F103">
         <v>1.5319586530413429E-3</v>
       </c>
@@ -3077,9 +2681,6 @@
       </c>
       <c r="H103">
         <v>2.5702554994335709E-3</v>
-      </c>
-      <c r="I103">
-        <v>0</v>
       </c>
       <c r="J103">
         <v>0.69318181818181823</v>
@@ -3107,9 +2708,6 @@
       <c r="H104">
         <v>-1.234184220187728E-3</v>
       </c>
-      <c r="I104">
-        <v>0</v>
-      </c>
       <c r="J104">
         <v>0.54681818181818176</v>
       </c>
@@ -3136,9 +2734,6 @@
       <c r="H105">
         <v>3.319194886401533E-3</v>
       </c>
-      <c r="I105">
-        <v>0</v>
-      </c>
       <c r="J105">
         <v>0.15000000000000011</v>
       </c>
@@ -3156,9 +2751,6 @@
       <c r="D106">
         <v>3.8627340104220309E-3</v>
       </c>
-      <c r="E106">
-        <v>4.5747109785033828</v>
-      </c>
       <c r="F106">
         <v>4.2914307498413962E-3</v>
       </c>
@@ -3167,9 +2759,6 @@
       </c>
       <c r="H106">
         <v>1.09999984419904E-2</v>
-      </c>
-      <c r="I106">
-        <v>2.306527293099592E-2</v>
       </c>
       <c r="J106">
         <v>0.14478260869565221</v>
@@ -3197,9 +2786,6 @@
       <c r="H107">
         <v>-1.343198581155391E-3</v>
       </c>
-      <c r="I107">
-        <v>0</v>
-      </c>
       <c r="J107">
         <v>6.0499999999999998E-2</v>
       </c>
@@ -3226,9 +2812,6 @@
       <c r="H108">
         <v>6.4757232631684758E-4</v>
       </c>
-      <c r="I108">
-        <v>0</v>
-      </c>
       <c r="J108">
         <v>0.1061904761904762</v>
       </c>
@@ -3246,9 +2829,6 @@
       <c r="D109">
         <v>7.1918942632311911E-3</v>
       </c>
-      <c r="E109">
-        <v>4.5315236458197932</v>
-      </c>
       <c r="F109">
         <v>6.2668190112002966E-3</v>
       </c>
@@ -3257,9 +2837,6 @@
       </c>
       <c r="H109">
         <v>8.1085090761305878E-3</v>
-      </c>
-      <c r="I109">
-        <v>0</v>
       </c>
       <c r="J109">
         <v>0.14600000000000021</v>
@@ -3287,9 +2864,6 @@
       <c r="H110">
         <v>6.1801473315625799E-3</v>
       </c>
-      <c r="I110">
-        <v>0</v>
-      </c>
       <c r="J110">
         <v>-1.0500000000000041E-2</v>
       </c>
@@ -3316,9 +2890,6 @@
       <c r="H111">
         <v>7.2474376369715543E-3</v>
       </c>
-      <c r="I111">
-        <v>0</v>
-      </c>
       <c r="J111">
         <v>9.9999999999999964E-2</v>
       </c>
@@ -3336,9 +2907,6 @@
       <c r="D112">
         <v>6.1334779168458198E-3</v>
       </c>
-      <c r="E112">
-        <v>4.5767707114663931</v>
-      </c>
       <c r="F112">
         <v>8.1503174787140864E-3</v>
       </c>
@@ -3347,9 +2915,6 @@
       </c>
       <c r="H112">
         <v>1.5124855899486529E-3</v>
-      </c>
-      <c r="I112">
-        <v>0</v>
       </c>
       <c r="J112">
         <v>0.14894736842105241</v>
@@ -3377,9 +2942,6 @@
       <c r="H113">
         <v>6.1783691617911529E-4</v>
       </c>
-      <c r="I113">
-        <v>0</v>
-      </c>
       <c r="J113">
         <v>0.1585714285714285</v>
       </c>
@@ -3406,9 +2968,6 @@
       <c r="H114">
         <v>7.087773176964518E-3</v>
       </c>
-      <c r="I114">
-        <v>0</v>
-      </c>
       <c r="J114">
         <v>-7.2000000000000064E-2</v>
       </c>
@@ -3426,9 +2985,6 @@
       <c r="D115">
         <v>1.420034556121053E-3</v>
       </c>
-      <c r="E115">
-        <v>4.526126978647639</v>
-      </c>
       <c r="F115">
         <v>6.1092829162934237E-3</v>
       </c>
@@ -3437,9 +2993,6 @@
       </c>
       <c r="H115">
         <v>7.8064577739827001E-3</v>
-      </c>
-      <c r="I115">
-        <v>0</v>
       </c>
       <c r="J115">
         <v>-0.27272727272727271</v>
@@ -3467,9 +3020,6 @@
       <c r="H116">
         <v>2.1105206580660511E-3</v>
       </c>
-      <c r="I116">
-        <v>0</v>
-      </c>
       <c r="J116">
         <v>-0.26450000000000012</v>
       </c>
@@ -3496,9 +3046,6 @@
       <c r="H117">
         <v>3.93477829983091E-3</v>
       </c>
-      <c r="I117">
-        <v>0</v>
-      </c>
       <c r="J117">
         <v>-0.1554545454545456</v>
       </c>
@@ -3516,9 +3063,6 @@
       <c r="D118">
         <v>2.989977017930912E-3</v>
       </c>
-      <c r="E118">
-        <v>4.526126978647639</v>
-      </c>
       <c r="F118">
         <v>3.7516507344932388E-3</v>
       </c>
@@ -3527,9 +3071,6 @@
       </c>
       <c r="H118">
         <v>1.0902539746586729E-2</v>
-      </c>
-      <c r="I118">
-        <v>0</v>
       </c>
       <c r="J118">
         <v>-7.7272727272728846E-3</v>
@@ -3557,9 +3098,6 @@
       <c r="H119">
         <v>-3.1216164410832188E-3</v>
       </c>
-      <c r="I119">
-        <v>0</v>
-      </c>
       <c r="J119">
         <v>1.5000000000000079E-2</v>
       </c>
@@ -3586,9 +3124,6 @@
       <c r="H120">
         <v>1.010544631152221E-2</v>
       </c>
-      <c r="I120">
-        <v>0</v>
-      </c>
       <c r="J120">
         <v>1.2173913043478431E-2</v>
       </c>
@@ -3606,9 +3141,6 @@
       <c r="D121">
         <v>3.8197642754766998E-3</v>
       </c>
-      <c r="E121">
-        <v>4.5185223792624187</v>
-      </c>
       <c r="F121">
         <v>4.5799195658826619E-3</v>
       </c>
@@ -3617,9 +3149,6 @@
       </c>
       <c r="H121">
         <v>2.8858382171428332E-3</v>
-      </c>
-      <c r="I121">
-        <v>0</v>
       </c>
       <c r="J121">
         <v>-4.999999999999992E-2</v>
@@ -3647,9 +3176,6 @@
       <c r="H122">
         <v>1.035749154873145E-3</v>
       </c>
-      <c r="I122">
-        <v>0</v>
-      </c>
       <c r="J122">
         <v>-0.16142857142857139</v>
       </c>
@@ -3676,9 +3202,6 @@
       <c r="H123">
         <v>4.7579744755523734E-3</v>
       </c>
-      <c r="I123">
-        <v>0</v>
-      </c>
       <c r="J123">
         <v>-0.29772727272727267</v>
       </c>
@@ -3696,9 +3219,6 @@
       <c r="D124">
         <v>3.7373011345192002E-3</v>
       </c>
-      <c r="E124">
-        <v>4.5870062153604207</v>
-      </c>
       <c r="F124">
         <v>4.1229639324118486E-3</v>
       </c>
@@ -3707,9 +3227,6 @@
       </c>
       <c r="H124">
         <v>5.6446034241854903E-3</v>
-      </c>
-      <c r="I124">
-        <v>0</v>
       </c>
       <c r="J124">
         <v>-0.22368421052631579</v>
@@ -3737,9 +3254,6 @@
       <c r="H125">
         <v>4.6864973047195946E-3</v>
       </c>
-      <c r="I125">
-        <v>5.6977434742540467E-2</v>
-      </c>
       <c r="J125">
         <v>-4.4500000000000033E-2</v>
       </c>
@@ -3766,9 +3280,6 @@
       <c r="H126">
         <v>4.1493194631527794E-3</v>
       </c>
-      <c r="I126">
-        <v>3.0305349495328929E-2</v>
-      </c>
       <c r="J126">
         <v>-8.3809523809523848E-2</v>
       </c>
@@ -3786,9 +3297,6 @@
       <c r="D127">
         <v>3.646727688089157E-3</v>
       </c>
-      <c r="E127">
-        <v>4.5163389722814751</v>
-      </c>
       <c r="F127">
         <v>3.9984059666959837E-3</v>
       </c>
@@ -3797,9 +3305,6 @@
       </c>
       <c r="H127">
         <v>4.6607068580879476E-3</v>
-      </c>
-      <c r="I127">
-        <v>0</v>
       </c>
       <c r="J127">
         <v>-0.1004761904761905</v>
@@ -3827,9 +3332,6 @@
       <c r="H128">
         <v>2.3273344490934988E-3</v>
       </c>
-      <c r="I128">
-        <v>0</v>
-      </c>
       <c r="J128">
         <v>-0.46761904761904782</v>
       </c>
@@ -3856,9 +3358,6 @@
       <c r="H129">
         <v>6.5105069774844537E-3</v>
       </c>
-      <c r="I129">
-        <v>0</v>
-      </c>
       <c r="J129">
         <v>-0.88476190476190464</v>
       </c>
@@ -3876,9 +3375,6 @@
       <c r="D130">
         <v>3.9368740745349129E-3</v>
       </c>
-      <c r="E130">
-        <v>4.4589876758100093</v>
-      </c>
       <c r="F130">
         <v>6.229440808738218E-3</v>
       </c>
@@ -3887,9 +3383,6 @@
       </c>
       <c r="H130">
         <v>8.3885515916204412E-3</v>
-      </c>
-      <c r="I130">
-        <v>0</v>
       </c>
       <c r="J130">
         <v>-0.84619047619047616</v>
@@ -3917,9 +3410,6 @@
       <c r="H131">
         <v>2.6569772955920001E-3</v>
       </c>
-      <c r="I131">
-        <v>0</v>
-      </c>
       <c r="J131">
         <v>-0.65714285714285714</v>
       </c>
@@ -3946,9 +3436,6 @@
       <c r="H132">
         <v>6.2547728791511048E-3</v>
       </c>
-      <c r="I132">
-        <v>0</v>
-      </c>
       <c r="J132">
         <v>-0.54318181818181821</v>
       </c>
@@ -3966,9 +3453,6 @@
       <c r="D133">
         <v>-4.9224019502069893E-4</v>
       </c>
-      <c r="E133">
-        <v>4.3782695857961693</v>
-      </c>
       <c r="F133">
         <v>1.059616114483575E-3</v>
       </c>
@@ -3977,9 +3461,6 @@
       </c>
       <c r="H133">
         <v>1.738712497024508E-3</v>
-      </c>
-      <c r="I133">
-        <v>0</v>
       </c>
       <c r="J133">
         <v>-0.74588235294117644</v>
@@ -4007,9 +3488,6 @@
       <c r="H134">
         <v>3.973734280847907E-3</v>
       </c>
-      <c r="I134">
-        <v>0</v>
-      </c>
       <c r="J134">
         <v>-0.51272727272727292</v>
       </c>
@@ -4036,9 +3514,6 @@
       <c r="H135">
         <v>-2.446561241251644E-3</v>
       </c>
-      <c r="I135">
-        <v>0</v>
-      </c>
       <c r="J135">
         <v>-0.30809523809523798</v>
       </c>
@@ -4056,9 +3531,6 @@
       <c r="D136">
         <v>1.8107682462638051E-3</v>
       </c>
-      <c r="E136">
-        <v>4.3579900568456402</v>
-      </c>
       <c r="F136">
         <v>1.7574696966455861E-3</v>
       </c>
@@ -4067,9 +3539,6 @@
       </c>
       <c r="H136">
         <v>2.16253835238156E-3</v>
-      </c>
-      <c r="I136">
-        <v>0</v>
       </c>
       <c r="J136">
         <v>-0.34833333333333311</v>
@@ -4097,9 +3566,6 @@
       <c r="H137">
         <v>6.6204448682327666E-4</v>
       </c>
-      <c r="I137">
-        <v>0</v>
-      </c>
       <c r="J137">
         <v>0.1071428571428573</v>
       </c>
@@ -4126,9 +3592,6 @@
       <c r="H138">
         <v>6.1930297873988849E-3</v>
       </c>
-      <c r="I138">
-        <v>0</v>
-      </c>
       <c r="J138">
         <v>0.33590909090909088</v>
       </c>
@@ -4146,9 +3609,6 @@
       <c r="D139">
         <v>-3.144480102355018E-3</v>
       </c>
-      <c r="E139">
-        <v>4.3228072750139104</v>
-      </c>
       <c r="F139">
         <v>2.109387553277386E-3</v>
       </c>
@@ -4157,9 +3617,6 @@
       </c>
       <c r="H139">
         <v>-2.576865977932385E-3</v>
-      </c>
-      <c r="I139">
-        <v>0</v>
       </c>
       <c r="J139">
         <v>0.15523809523809531</v>
@@ -4187,9 +3644,6 @@
       <c r="H140">
         <v>3.3524023542881309E-3</v>
       </c>
-      <c r="I140">
-        <v>0</v>
-      </c>
       <c r="J140">
         <v>0.2936363636363637</v>
       </c>
@@ -4216,9 +3670,6 @@
       <c r="H141">
         <v>6.7461649312949854E-3</v>
       </c>
-      <c r="I141">
-        <v>-1.201215644800357E-2</v>
-      </c>
       <c r="J141">
         <v>0.35500000000000009</v>
       </c>
@@ -4236,9 +3687,6 @@
       <c r="D142">
         <v>-1.633918245046218E-3</v>
       </c>
-      <c r="E142">
-        <v>4.3515674271891731</v>
-      </c>
       <c r="F142">
         <v>1.9630505639245399E-3</v>
       </c>
@@ -4247,9 +3695,6 @@
       </c>
       <c r="H142">
         <v>6.4696892092506184E-3</v>
-      </c>
-      <c r="I142">
-        <v>0</v>
       </c>
       <c r="J142">
         <v>0.54238095238095241</v>
@@ -4277,9 +3722,6 @@
       <c r="H143">
         <v>-2.8686290513153519E-3</v>
       </c>
-      <c r="I143">
-        <v>0</v>
-      </c>
       <c r="J143">
         <v>0.6623809523809524</v>
       </c>
@@ -4306,9 +3748,6 @@
       <c r="H144">
         <v>-1.2189432736793291E-3</v>
       </c>
-      <c r="I144">
-        <v>0</v>
-      </c>
       <c r="J144">
         <v>0.90047619047619043</v>
       </c>
@@ -4326,9 +3765,6 @@
       <c r="D145">
         <v>-1.5894419013555709E-3</v>
       </c>
-      <c r="E145">
-        <v>4.282206299391671</v>
-      </c>
       <c r="F145">
         <v>-4.0065106332853873E-4</v>
       </c>
@@ -4337,9 +3773,6 @@
       </c>
       <c r="H145">
         <v>1.3535689051416E-3</v>
-      </c>
-      <c r="I145">
-        <v>0</v>
       </c>
       <c r="J145">
         <v>1.3294444444444451</v>
@@ -4367,9 +3800,6 @@
       <c r="H146">
         <v>-2.85209585104873E-3</v>
       </c>
-      <c r="I146">
-        <v>7.2812355474967561E-2</v>
-      </c>
       <c r="J146">
         <v>1.393636363636364</v>
       </c>
@@ -4396,9 +3826,6 @@
       <c r="H147">
         <v>5.6831420539076296E-3</v>
       </c>
-      <c r="I147">
-        <v>0</v>
-      </c>
       <c r="J147">
         <v>1.671</v>
       </c>
@@ -4416,9 +3843,6 @@
       <c r="D148">
         <v>-8.1879275001917051E-4</v>
       </c>
-      <c r="E148">
-        <v>4.3579900568456402</v>
-      </c>
       <c r="F148">
         <v>1.0386528124186609E-3</v>
       </c>
@@ -4427,9 +3851,6 @@
       </c>
       <c r="H148">
         <v>1.9792340445867751E-3</v>
-      </c>
-      <c r="I148">
-        <v>0</v>
       </c>
       <c r="J148">
         <v>2.2272222222222222</v>
@@ -4457,9 +3878,6 @@
       <c r="H149">
         <v>6.3731120372558792E-3</v>
       </c>
-      <c r="I149">
-        <v>0</v>
-      </c>
       <c r="J149">
         <v>2.0160869565217392</v>
       </c>
@@ -4486,9 +3904,6 @@
       <c r="H150">
         <v>3.6197439425986739E-3</v>
       </c>
-      <c r="I150">
-        <v>0</v>
-      </c>
       <c r="J150">
         <v>1.529047619047619</v>
       </c>
@@ -4506,9 +3921,6 @@
       <c r="D151">
         <v>2.9659222068012529E-3</v>
       </c>
-      <c r="E151">
-        <v>4.3845235148724688</v>
-      </c>
       <c r="F151">
         <v>4.0722262142693921E-3</v>
       </c>
@@ -4517,9 +3929,6 @@
       </c>
       <c r="H151">
         <v>3.8248100730431389E-3</v>
-      </c>
-      <c r="I151">
-        <v>0</v>
       </c>
       <c r="J151">
         <v>1.3565</v>
@@ -4547,9 +3956,6 @@
       <c r="H152">
         <v>1.3919901578933751E-3</v>
       </c>
-      <c r="I152">
-        <v>0</v>
-      </c>
       <c r="J152">
         <v>0.87954545454545463</v>
       </c>
@@ -4576,9 +3982,6 @@
       <c r="H153">
         <v>3.8366201068633639E-3</v>
       </c>
-      <c r="I153">
-        <v>0</v>
-      </c>
       <c r="J153">
         <v>0.6880952380952382</v>
       </c>
@@ -4596,9 +3999,6 @@
       <c r="D154">
         <v>8.129625924304662E-4</v>
       </c>
-      <c r="E154">
-        <v>4.4079380164583828</v>
-      </c>
       <c r="F154">
         <v>3.7809995159356902E-3</v>
       </c>
@@ -4607,9 +4007,6 @@
       </c>
       <c r="H154">
         <v>7.0838623408828738E-3</v>
-      </c>
-      <c r="I154">
-        <v>0</v>
       </c>
       <c r="J154">
         <v>0.77863636363636379</v>
@@ -4637,9 +4034,6 @@
       <c r="H155">
         <v>1.6607241084365401E-3</v>
       </c>
-      <c r="I155">
-        <v>0</v>
-      </c>
       <c r="J155">
         <v>0.73142857142857143</v>
       </c>
@@ -4666,9 +4060,6 @@
       <c r="H156">
         <v>9.5088513223906546E-4</v>
       </c>
-      <c r="I156">
-        <v>0</v>
-      </c>
       <c r="J156">
         <v>1.013157894736842</v>
       </c>
@@ -4686,9 +4077,6 @@
       <c r="D157">
         <v>2.85736383245272E-3</v>
       </c>
-      <c r="E157">
-        <v>4.4067192472642533</v>
-      </c>
       <c r="F157">
         <v>4.1439851139752903E-3</v>
       </c>
@@ -4697,9 +4085,6 @@
       </c>
       <c r="H157">
         <v>-2.6493493028567632E-3</v>
-      </c>
-      <c r="I157">
-        <v>0</v>
       </c>
       <c r="J157">
         <v>1.1435</v>
@@ -4727,9 +4112,6 @@
       <c r="H158">
         <v>3.5288189186886139E-3</v>
       </c>
-      <c r="I158">
-        <v>0</v>
-      </c>
       <c r="J158">
         <v>1.321818181818182</v>
       </c>
@@ -4756,9 +4138,6 @@
       <c r="H159">
         <v>3.7599732738655689E-3</v>
       </c>
-      <c r="I159">
-        <v>0</v>
-      </c>
       <c r="J159">
         <v>1.6695238095238101</v>
       </c>
@@ -4776,9 +4155,6 @@
       <c r="D160">
         <v>2.8534229397116921E-3</v>
       </c>
-      <c r="E160">
-        <v>4.5304466397921548</v>
-      </c>
       <c r="F160">
         <v>5.6160619641403287E-3</v>
       </c>
@@ -4787,9 +4163,6 @@
       </c>
       <c r="H160">
         <v>-1.393482415629421E-3</v>
-      </c>
-      <c r="I160">
-        <v>0</v>
       </c>
       <c r="J160">
         <v>1.8089999999999999</v>
@@ -4817,9 +4190,6 @@
       <c r="H161">
         <v>2.0177323606009878E-3</v>
       </c>
-      <c r="I161">
-        <v>0</v>
-      </c>
       <c r="J161">
         <v>1.3986363636363639</v>
       </c>
@@ -4846,9 +4216,6 @@
       <c r="H162">
         <v>5.0374569146853787E-3</v>
       </c>
-      <c r="I162">
-        <v>0</v>
-      </c>
       <c r="J162">
         <v>1.23</v>
       </c>
@@ -4866,9 +4233,6 @@
       <c r="D163">
         <v>4.1873880500524763E-3</v>
       </c>
-      <c r="E163">
-        <v>4.4841318576110352</v>
-      </c>
       <c r="F163">
         <v>4.1800516232424201E-3</v>
       </c>
@@ -4877,9 +4241,6 @@
       </c>
       <c r="H163">
         <v>6.3350014495480167E-3</v>
-      </c>
-      <c r="I163">
-        <v>0</v>
       </c>
       <c r="J163">
         <v>1.4854545454545449</v>
@@ -4907,9 +4268,6 @@
       <c r="H164">
         <v>1.307181668552815E-3</v>
       </c>
-      <c r="I164">
-        <v>0</v>
-      </c>
       <c r="J164">
         <v>1.178181818181818</v>
       </c>
@@ -4936,9 +4294,6 @@
       <c r="H165">
         <v>6.6834525444825488E-4</v>
       </c>
-      <c r="I165">
-        <v>0</v>
-      </c>
       <c r="J165">
         <v>1.1485000000000001</v>
       </c>
@@ -4956,9 +4311,6 @@
       <c r="D166">
         <v>5.8437771983719236E-3</v>
       </c>
-      <c r="E166">
-        <v>4.5559799417973199</v>
-      </c>
       <c r="F166">
         <v>9.9453028690099643E-3</v>
       </c>
@@ -4967,9 +4319,6 @@
       </c>
       <c r="H166">
         <v>9.2629505662671363E-3</v>
-      </c>
-      <c r="I166">
-        <v>0</v>
       </c>
       <c r="J166">
         <v>1.227391304347826</v>
@@ -4997,9 +4346,6 @@
       <c r="H167">
         <v>6.1977040698675268E-3</v>
       </c>
-      <c r="I167">
-        <v>0</v>
-      </c>
       <c r="J167">
         <v>1.0255000000000001</v>
       </c>
@@ -5026,9 +4372,6 @@
       <c r="H168">
         <v>4.5779336821176742E-3</v>
       </c>
-      <c r="I168">
-        <v>0</v>
-      </c>
       <c r="J168">
         <v>0.95800000000000018</v>
       </c>
@@ -5046,9 +4389,6 @@
       <c r="D169">
         <v>3.9960760708179777E-3</v>
       </c>
-      <c r="E169">
-        <v>4.5075573571210912</v>
-      </c>
       <c r="F169">
         <v>7.3759958257522129E-3</v>
       </c>
@@ -5057,9 +4397,6 @@
       </c>
       <c r="H169">
         <v>5.5044160654169616E-3</v>
-      </c>
-      <c r="I169">
-        <v>0</v>
       </c>
       <c r="J169">
         <v>1.0069999999999999</v>
@@ -5087,9 +4424,6 @@
       <c r="H170">
         <v>1.0918603503622391E-3</v>
       </c>
-      <c r="I170">
-        <v>0</v>
-      </c>
       <c r="J170">
         <v>0.84000000000000008</v>
       </c>
@@ -5116,9 +4450,6 @@
       <c r="H171">
         <v>9.1423904732721439E-3</v>
       </c>
-      <c r="I171">
-        <v>0</v>
-      </c>
       <c r="J171">
         <v>0.57318181818181813</v>
       </c>
@@ -5136,9 +4467,6 @@
       <c r="D172">
         <v>5.2364082165734516E-3</v>
       </c>
-      <c r="E172">
-        <v>4.4054989908590239</v>
-      </c>
       <c r="F172">
         <v>3.8093596738590918E-3</v>
       </c>
@@ -5147,9 +4475,6 @@
       </c>
       <c r="H172">
         <v>5.3655095583202686E-3</v>
-      </c>
-      <c r="I172">
-        <v>0</v>
       </c>
       <c r="J172">
         <v>0.4466666666666666</v>
@@ -5177,9 +4502,6 @@
       <c r="H173">
         <v>3.3318885180531051E-3</v>
       </c>
-      <c r="I173">
-        <v>0</v>
-      </c>
       <c r="J173">
         <v>-0.14090909090909079</v>
       </c>
@@ -5206,9 +4528,6 @@
       <c r="H174">
         <v>5.0247265638656557E-3</v>
       </c>
-      <c r="I174">
-        <v>0</v>
-      </c>
       <c r="J174">
         <v>-0.17799999999999991</v>
       </c>
@@ -5226,9 +4545,6 @@
       <c r="D175">
         <v>2.5211798884576808E-3</v>
       </c>
-      <c r="E175">
-        <v>4.3438054218536841</v>
-      </c>
       <c r="F175">
         <v>3.6721496929654758E-3</v>
       </c>
@@ -5237,9 +4553,6 @@
       </c>
       <c r="H175">
         <v>3.9611135000257036E-3</v>
-      </c>
-      <c r="I175">
-        <v>0</v>
       </c>
       <c r="J175">
         <v>-4.6363636363636433E-2</v>
@@ -5267,9 +4580,6 @@
       <c r="H176">
         <v>6.3482486454766729E-3</v>
       </c>
-      <c r="I176">
-        <v>0</v>
-      </c>
       <c r="J176">
         <v>-0.40761904761904771</v>
       </c>
@@ -5296,9 +4606,6 @@
       <c r="H177">
         <v>5.6883978223680742E-3</v>
       </c>
-      <c r="I177">
-        <v>0</v>
-      </c>
       <c r="J177">
         <v>-1.2580952380952379</v>
       </c>
@@ -5316,9 +4623,6 @@
       <c r="D178">
         <v>3.3099503872655589E-3</v>
       </c>
-      <c r="E178">
-        <v>4.2766661190160553</v>
-      </c>
       <c r="F178">
         <v>-4.0154561515599596E-3</v>
       </c>
@@ -5327,9 +4631,6 @@
       </c>
       <c r="H178">
         <v>-1.4717725392117129E-3</v>
-      </c>
-      <c r="I178">
-        <v>0.19117735925171719</v>
       </c>
       <c r="J178">
         <v>-1.417826086956522</v>
@@ -5357,9 +4658,6 @@
       <c r="H179">
         <v>3.193304133100483E-3</v>
       </c>
-      <c r="I179">
-        <v>0</v>
-      </c>
       <c r="J179">
         <v>-1.215789473684211</v>
       </c>
@@ -5386,9 +4684,6 @@
       <c r="H180">
         <v>6.4148172038027704E-3</v>
       </c>
-      <c r="I180">
-        <v>0</v>
-      </c>
       <c r="J180">
         <v>-0.60190476190476183</v>
       </c>
@@ -5406,9 +4701,6 @@
       <c r="D181">
         <v>4.0250300278739104E-3</v>
       </c>
-      <c r="E181">
-        <v>4.3372907408324899</v>
-      </c>
       <c r="F181">
         <v>2.3012989907069681E-3</v>
       </c>
@@ -5417,9 +4709,6 @@
       </c>
       <c r="H181">
         <v>8.9697170703271212E-3</v>
-      </c>
-      <c r="I181">
-        <v>0</v>
       </c>
       <c r="J181">
         <v>-0.84050000000000014</v>
@@ -5447,9 +4736,6 @@
       <c r="H182">
         <v>8.1830848781958565E-3</v>
       </c>
-      <c r="I182">
-        <v>0</v>
-      </c>
       <c r="J182">
         <v>-0.52684210526315778</v>
       </c>
@@ -5476,9 +4762,6 @@
       <c r="H183">
         <v>3.1399447638662541E-3</v>
       </c>
-      <c r="I183">
-        <v>0.85258712891672395</v>
-      </c>
       <c r="J183">
         <v>-0.43227272727272742</v>
       </c>
@@ -5496,9 +4779,6 @@
       <c r="D184">
         <v>1.9698894789925698E-3</v>
       </c>
-      <c r="E184">
-        <v>4.1239033644636454</v>
-      </c>
       <c r="F184">
         <v>-6.4930324420089391E-3</v>
       </c>
@@ -5507,9 +4787,6 @@
       </c>
       <c r="H184">
         <v>2.1307194126638511E-3</v>
-      </c>
-      <c r="I184">
-        <v>0</v>
       </c>
       <c r="J184">
         <v>7.3888888888888796E-2</v>
@@ -5537,9 +4814,6 @@
       <c r="H185">
         <v>7.2692631813104924E-3</v>
       </c>
-      <c r="I185">
-        <v>0</v>
-      </c>
       <c r="J185">
         <v>-0.55047619047619079</v>
       </c>
@@ -5566,9 +4840,6 @@
       <c r="H186">
         <v>3.6197529258039651E-3</v>
       </c>
-      <c r="I186">
-        <v>0</v>
-      </c>
       <c r="J186">
         <v>-1.10952380952381</v>
       </c>
@@ -5586,9 +4857,6 @@
       <c r="D187">
         <v>2.1283247164571861E-3</v>
       </c>
-      <c r="E187">
-        <v>4.2780540442909034</v>
-      </c>
       <c r="F187">
         <v>6.6564603402952116E-4</v>
       </c>
@@ -5597,9 +4865,6 @@
       </c>
       <c r="H187">
         <v>7.0644590462975998E-3</v>
-      </c>
-      <c r="I187">
-        <v>0</v>
       </c>
       <c r="J187">
         <v>-1.206363636363637</v>
@@ -5627,9 +4892,6 @@
       <c r="H188">
         <v>5.7046314154689526E-3</v>
       </c>
-      <c r="I188">
-        <v>0</v>
-      </c>
       <c r="J188">
         <v>-1.1339999999999999</v>
       </c>
@@ -5656,9 +4918,6 @@
       <c r="H189">
         <v>1.4766616488532951E-3</v>
       </c>
-      <c r="I189">
-        <v>0</v>
-      </c>
       <c r="J189">
         <v>-0.9900000000000001</v>
       </c>
@@ -5676,9 +4935,6 @@
       <c r="D190">
         <v>-2.1620934235855321E-4</v>
       </c>
-      <c r="E190">
-        <v>4.165113633110308</v>
-      </c>
       <c r="F190">
         <v>-1.420076567749007E-3</v>
       </c>
@@ -5687,9 +4943,6 @@
       </c>
       <c r="H190">
         <v>-2.8351495357181729E-3</v>
-      </c>
-      <c r="I190">
-        <v>0</v>
       </c>
       <c r="J190">
         <v>-1.3186363636363641</v>
@@ -5717,9 +4970,6 @@
       <c r="H191">
         <v>5.4242738060636952E-3</v>
       </c>
-      <c r="I191">
-        <v>0</v>
-      </c>
       <c r="J191">
         <v>-0.83700000000000008</v>
       </c>
@@ -5746,9 +4996,6 @@
       <c r="H192">
         <v>7.0063674392280006E-3</v>
       </c>
-      <c r="I192">
-        <v>9.881092392078461E-2</v>
-      </c>
       <c r="J192">
         <v>-0.14909090909090919</v>
       </c>
@@ -5766,9 +5013,6 @@
       <c r="D193">
         <v>-4.6528016632390026E-3</v>
       </c>
-      <c r="E193">
-        <v>4.0859763125515842</v>
-      </c>
       <c r="F193">
         <v>-7.861693220295507E-3</v>
       </c>
@@ -5777,9 +5021,6 @@
       </c>
       <c r="H193">
         <v>5.4273029303448794E-3</v>
-      </c>
-      <c r="I193">
-        <v>0</v>
       </c>
       <c r="J193">
         <v>2.5555555555555401E-2</v>
@@ -5807,9 +5048,6 @@
       <c r="H194">
         <v>9.6167635424819764E-3</v>
       </c>
-      <c r="I194">
-        <v>0</v>
-      </c>
       <c r="J194">
         <v>0.1276190476190476</v>
       </c>
@@ -5836,9 +5074,6 @@
       <c r="H195">
         <v>-1.1316103888550091E-3</v>
       </c>
-      <c r="I195">
-        <v>0</v>
-      </c>
       <c r="J195">
         <v>0.66909090909090907</v>
       </c>
@@ -5856,9 +5091,6 @@
       <c r="D196">
         <v>-4.8634758761476604E-3</v>
       </c>
-      <c r="E196">
-        <v>4.0535225677018456</v>
-      </c>
       <c r="F196">
         <v>-4.6028962132886866E-3</v>
       </c>
@@ -5867,9 +5099,6 @@
       </c>
       <c r="H196">
         <v>-6.3822412491347791E-3</v>
-      </c>
-      <c r="I196">
-        <v>0</v>
       </c>
       <c r="J196">
         <v>1.407777777777778</v>
@@ -5897,9 +5126,6 @@
       <c r="H197">
         <v>-8.1084908588469062E-3</v>
       </c>
-      <c r="I197">
-        <v>0</v>
-      </c>
       <c r="J197">
         <v>1.623</v>
       </c>
@@ -5926,9 +5152,6 @@
       <c r="H198">
         <v>-1.6650856036584121E-3</v>
       </c>
-      <c r="I198">
-        <v>0</v>
-      </c>
       <c r="J198">
         <v>1.322727272727273</v>
       </c>
@@ -5946,9 +5169,6 @@
       <c r="D199">
         <v>2.1426153319872299E-3</v>
       </c>
-      <c r="E199">
-        <v>4.28771595520264</v>
-      </c>
       <c r="F199">
         <v>5.2843264649258259E-3</v>
       </c>
@@ -5957,9 +5177,6 @@
       </c>
       <c r="H199">
         <v>-7.4325942648183494E-3</v>
-      </c>
-      <c r="I199">
-        <v>0</v>
       </c>
       <c r="J199">
         <v>1.67</v>
@@ -5987,9 +5204,6 @@
       <c r="H200">
         <v>-6.0931337954848166E-3</v>
       </c>
-      <c r="I200">
-        <v>0</v>
-      </c>
       <c r="J200">
         <v>1.573809523809524</v>
       </c>
@@ -6016,9 +5230,6 @@
       <c r="H201">
         <v>-1.727706769127479E-3</v>
       </c>
-      <c r="I201">
-        <v>0</v>
-      </c>
       <c r="J201">
         <v>0.9486363636363635</v>
       </c>
@@ -6036,9 +5247,6 @@
       <c r="D202">
         <v>4.9765245017479032E-3</v>
       </c>
-      <c r="E202">
-        <v>4.3267781604434026</v>
-      </c>
       <c r="F202">
         <v>8.419405295777338E-3</v>
       </c>
@@ -6047,9 +5255,6 @@
       </c>
       <c r="H202">
         <v>-1.118144519413278E-3</v>
-      </c>
-      <c r="I202">
-        <v>0</v>
       </c>
       <c r="J202">
         <v>0.69571428571428584</v>
@@ -6077,9 +5282,6 @@
       <c r="H203">
         <v>-6.5110755967445755E-4</v>
       </c>
-      <c r="I203">
-        <v>0</v>
-      </c>
       <c r="J203">
         <v>0.67666666666666675</v>
       </c>
@@ -6106,9 +5308,6 @@
       <c r="H204">
         <v>3.1058081809138831E-3</v>
       </c>
-      <c r="I204">
-        <v>0</v>
-      </c>
       <c r="J204">
         <v>1.187272727272727</v>
       </c>
@@ -6126,9 +5325,6 @@
       <c r="D205">
         <v>1.8682563011811479E-3</v>
       </c>
-      <c r="E205">
-        <v>4.3254562831854866</v>
-      </c>
       <c r="F205">
         <v>2.1893702698019268E-3</v>
       </c>
@@ -6137,9 +5333,6 @@
       </c>
       <c r="H205">
         <v>-4.0067699564971804E-3</v>
-      </c>
-      <c r="I205">
-        <v>0</v>
       </c>
       <c r="J205">
         <v>1.5658823529411769</v>
@@ -6167,9 +5360,6 @@
       <c r="H206">
         <v>-2.6745991281842412E-3</v>
       </c>
-      <c r="I206">
-        <v>0</v>
-      </c>
       <c r="J206">
         <v>1.395909090909091</v>
       </c>
@@ -6196,9 +5386,6 @@
       <c r="H207">
         <v>3.0177215594235922E-3</v>
       </c>
-      <c r="I207">
-        <v>0</v>
-      </c>
       <c r="J207">
         <v>1.936666666666667</v>
       </c>
@@ -6216,9 +5403,6 @@
       <c r="D208">
         <v>3.9791813194902659E-3</v>
       </c>
-      <c r="E208">
-        <v>4.437934266612177</v>
-      </c>
       <c r="F208">
         <v>6.5449127674952479E-3</v>
       </c>
@@ -6227,9 +5411,6 @@
       </c>
       <c r="H208">
         <v>5.545257542211246E-3</v>
-      </c>
-      <c r="I208">
-        <v>7.5067573033422708E-2</v>
       </c>
       <c r="J208">
         <v>1.885</v>
@@ -6257,9 +5438,6 @@
       <c r="H209">
         <v>3.6406944122155949E-3</v>
       </c>
-      <c r="I209">
-        <v>5.8019226161079018E-3</v>
-      </c>
       <c r="J209">
         <v>1.5230434782608699</v>
       </c>
@@ -6286,9 +5464,6 @@
       <c r="H210">
         <v>5.1701516088247246E-3</v>
       </c>
-      <c r="I210">
-        <v>5.7684543967404522E-3</v>
-      </c>
       <c r="J210">
         <v>1.6409523809523809</v>
       </c>
@@ -6306,9 +5481,6 @@
       <c r="D211">
         <v>2.5220045025342591E-4</v>
       </c>
-      <c r="E211">
-        <v>4.4224485491727972</v>
-      </c>
       <c r="F211">
         <v>3.0645080848845652E-3</v>
       </c>
@@ -6317,9 +5489,6 @@
       </c>
       <c r="H211">
         <v>4.9597839766946086E-3</v>
-      </c>
-      <c r="I211">
-        <v>0</v>
       </c>
       <c r="J211">
         <v>1.4935</v>
@@ -6347,9 +5516,6 @@
       <c r="H212">
         <v>8.3974283951135931E-3</v>
       </c>
-      <c r="I212">
-        <v>0</v>
-      </c>
       <c r="J212">
         <v>1.340454545454546</v>
       </c>
@@ -6376,9 +5542,6 @@
       <c r="H213">
         <v>5.2954587183613464E-3</v>
       </c>
-      <c r="I213">
-        <v>0</v>
-      </c>
       <c r="J213">
         <v>1.631428571428571</v>
       </c>
@@ -6396,9 +5559,6 @@
       <c r="D214">
         <v>1.9717308006157448E-3</v>
       </c>
-      <c r="E214">
-        <v>4.4964707690647501</v>
-      </c>
       <c r="F214">
         <v>3.855220024433947E-3</v>
       </c>
@@ -6407,9 +5567,6 @@
       </c>
       <c r="H214">
         <v>2.1664903022422521E-3</v>
-      </c>
-      <c r="I214">
-        <v>0</v>
       </c>
       <c r="J214">
         <v>1.7659090909090911</v>
@@ -6437,9 +5594,6 @@
       <c r="H215">
         <v>7.9795391532933024E-3</v>
       </c>
-      <c r="I215">
-        <v>0.13291493313721009</v>
-      </c>
       <c r="J215">
         <v>1.75</v>
       </c>
@@ -6466,9 +5620,6 @@
       <c r="H216">
         <v>4.5632121144087989E-3</v>
       </c>
-      <c r="I216">
-        <v>0</v>
-      </c>
       <c r="J216">
         <v>1.9145000000000001</v>
       </c>
@@ -6486,9 +5637,6 @@
       <c r="D217">
         <v>4.1086282672715413E-3</v>
       </c>
-      <c r="E217">
-        <v>4.4659081186545837</v>
-      </c>
       <c r="F217">
         <v>8.2186134267043798E-3</v>
       </c>
@@ -6497,9 +5645,6 @@
       </c>
       <c r="H217">
         <v>3.139740593461227E-3</v>
-      </c>
-      <c r="I217">
-        <v>0</v>
       </c>
       <c r="J217">
         <v>1.996842105263158</v>
@@ -6527,9 +5672,6 @@
       <c r="H218">
         <v>3.4666384175370268E-3</v>
       </c>
-      <c r="I218">
-        <v>0</v>
-      </c>
       <c r="J218">
         <v>1.9759090909090911</v>
       </c>
@@ -6556,9 +5698,6 @@
       <c r="H219">
         <v>3.531383910702957E-3</v>
       </c>
-      <c r="I219">
-        <v>0</v>
-      </c>
       <c r="J219">
         <v>1.922380952380953</v>
       </c>
@@ -6576,9 +5715,6 @@
       <c r="D220">
         <v>3.6863436888534551E-3</v>
       </c>
-      <c r="E220">
-        <v>4.467056883858457</v>
-      </c>
       <c r="F220">
         <v>3.6116753272104059E-3</v>
       </c>
@@ -6587,9 +5723,6 @@
       </c>
       <c r="H220">
         <v>2.247019748972789E-3</v>
-      </c>
-      <c r="I220">
-        <v>0</v>
       </c>
       <c r="J220">
         <v>1.9236842105263161</v>
@@ -6617,9 +5750,6 @@
       <c r="H221">
         <v>3.0119080489399148E-3</v>
       </c>
-      <c r="I221">
-        <v>0</v>
-      </c>
       <c r="J221">
         <v>1.9595652173913041</v>
       </c>
@@ -6646,9 +5776,6 @@
       <c r="H222">
         <v>4.5118661240888258E-3</v>
       </c>
-      <c r="I222">
-        <v>0</v>
-      </c>
       <c r="J222">
         <v>1.9295</v>
       </c>
@@ -6666,9 +5793,6 @@
       <c r="D223">
         <v>4.3951821498353638E-3</v>
       </c>
-      <c r="E223">
-        <v>4.5020294270685781</v>
-      </c>
       <c r="F223">
         <v>5.2271639370431444E-3</v>
       </c>
@@ -6677,9 +5801,6 @@
       </c>
       <c r="H223">
         <v>3.1819216710591292E-3</v>
-      </c>
-      <c r="I223">
-        <v>0</v>
       </c>
       <c r="J223">
         <v>1.612857142857143</v>
@@ -6707,9 +5828,6 @@
       <c r="H224">
         <v>3.143679383660114E-3</v>
       </c>
-      <c r="I224">
-        <v>0</v>
-      </c>
       <c r="J224">
         <v>1.4772727272727271</v>
       </c>
@@ -6736,9 +5854,6 @@
       <c r="H225">
         <v>4.1524724833443827E-3</v>
       </c>
-      <c r="I225">
-        <v>0</v>
-      </c>
       <c r="J225">
         <v>1.3931578947368419</v>
       </c>
@@ -6756,9 +5871,6 @@
       <c r="D226">
         <v>2.9052091147345749E-3</v>
       </c>
-      <c r="E226">
-        <v>4.4886363697321396</v>
-      </c>
       <c r="F226">
         <v>2.780726222024299E-3</v>
       </c>
@@ -6767,9 +5879,6 @@
       </c>
       <c r="H226">
         <v>6.3725671606107426E-3</v>
-      </c>
-      <c r="I226">
-        <v>6.611102511206246E-2</v>
       </c>
       <c r="J226">
         <v>1.026956521739131</v>
@@ -6797,9 +5906,6 @@
       <c r="H227">
         <v>7.1107149132494376E-3</v>
       </c>
-      <c r="I227">
-        <v>0</v>
-      </c>
       <c r="J227">
         <v>0.81714285714285717</v>
       </c>
@@ -6826,9 +5932,6 @@
       <c r="H228">
         <v>9.8389152711853001E-4</v>
       </c>
-      <c r="I228">
-        <v>0</v>
-      </c>
       <c r="J228">
         <v>0.55850000000000011</v>
       </c>
@@ -6846,9 +5949,6 @@
       <c r="D229">
         <v>4.4411972530653543E-3</v>
       </c>
-      <c r="E229">
-        <v>4.4355674016019124</v>
-      </c>
       <c r="F229">
         <v>6.2348103259157739E-3</v>
       </c>
@@ -6857,9 +5957,6 @@
       </c>
       <c r="H229">
         <v>4.8437469411961587E-3</v>
-      </c>
-      <c r="I229">
-        <v>0</v>
       </c>
       <c r="J229">
         <v>0.62263157894736831</v>
@@ -6887,9 +5984,6 @@
       <c r="H230">
         <v>4.9646765349429236E-3</v>
       </c>
-      <c r="I230">
-        <v>0</v>
-      </c>
       <c r="J230">
         <v>0.72761904761904772</v>
       </c>
@@ -6919,9 +6013,6 @@
       <c r="H231">
         <v>4.5886211435846036E-3</v>
       </c>
-      <c r="I231">
-        <v>0</v>
-      </c>
       <c r="J231">
         <v>0.67285714285714293</v>
       </c>
@@ -6951,9 +6042,6 @@
       <c r="H232">
         <v>4.1436420992315703E-3</v>
       </c>
-      <c r="I232">
-        <v>0</v>
-      </c>
       <c r="J232">
         <v>0.69555555555555548</v>
       </c>
@@ -6983,9 +6071,6 @@
       <c r="H233">
         <v>8.7605563235921835E-3</v>
       </c>
-      <c r="I233">
-        <v>0</v>
-      </c>
       <c r="J233">
         <v>0.72545454545454524</v>
       </c>
@@ -7015,9 +6100,6 @@
       <c r="H234">
         <v>8.8686145386045467E-3</v>
       </c>
-      <c r="I234">
-        <v>0</v>
-      </c>
       <c r="J234">
         <v>0.69950000000000023</v>
       </c>
@@ -7047,9 +6129,6 @@
       <c r="H235">
         <v>4.2668884587442344E-3</v>
       </c>
-      <c r="I235">
-        <v>0</v>
-      </c>
       <c r="J235">
         <v>0.52571428571428569</v>
       </c>
@@ -7079,9 +6158,6 @@
       <c r="H236">
         <v>3.161207840536306E-3</v>
       </c>
-      <c r="I236">
-        <v>0</v>
-      </c>
       <c r="J236">
         <v>0.36772727272727279</v>
       </c>
@@ -7111,9 +6187,6 @@
       <c r="H237">
         <v>1.8583358051493799E-3</v>
       </c>
-      <c r="I237">
-        <v>0</v>
-      </c>
       <c r="J237">
         <v>0.24849999999999989</v>
       </c>
@@ -7143,9 +6216,6 @@
       <c r="H238">
         <v>4.7269467203960858E-3</v>
       </c>
-      <c r="I238">
-        <v>0</v>
-      </c>
       <c r="J238">
         <v>9.8260869565217457E-2</v>
       </c>
@@ -7175,9 +6245,6 @@
       <c r="H239">
         <v>2.2681252359628701E-3</v>
       </c>
-      <c r="I239">
-        <v>0</v>
-      </c>
       <c r="J239">
         <v>-0.22199999999999989</v>
       </c>
@@ -7207,9 +6274,6 @@
       <c r="H240">
         <v>5.4671702684245824E-3</v>
       </c>
-      <c r="I240">
-        <v>0</v>
-      </c>
       <c r="J240">
         <v>-0.49428571428571427</v>
       </c>
@@ -7239,9 +6303,6 @@
       <c r="H241">
         <v>6.4472028868980402E-3</v>
       </c>
-      <c r="I241">
-        <v>0</v>
-      </c>
       <c r="J241">
         <v>-1.2090000000000001</v>
       </c>
@@ -7271,9 +6332,6 @@
       <c r="H242">
         <v>6.598956285760238E-3</v>
       </c>
-      <c r="I242">
-        <v>0</v>
-      </c>
       <c r="J242">
         <v>-1.2889999999999999</v>
       </c>
@@ -7303,9 +6361,6 @@
       <c r="H243">
         <v>6.2162564068142254E-3</v>
       </c>
-      <c r="I243">
-        <v>0</v>
-      </c>
       <c r="J243">
         <v>-1.3149999999999999</v>
       </c>
@@ -7335,9 +6390,6 @@
       <c r="H244">
         <v>4.4894000453492566E-3</v>
       </c>
-      <c r="I244">
-        <v>6.51696350745814E-2</v>
-      </c>
       <c r="J244">
         <v>-1.1383333333333341</v>
       </c>
@@ -7367,9 +6419,6 @@
       <c r="H245">
         <v>1.0920378347272219E-3</v>
       </c>
-      <c r="I245">
-        <v>0</v>
-      </c>
       <c r="J245">
         <v>-1.132272727272728</v>
       </c>
@@ -7399,9 +6448,6 @@
       <c r="H246">
         <v>5.7677447229647072E-3</v>
       </c>
-      <c r="I246">
-        <v>0</v>
-      </c>
       <c r="J246">
         <v>-0.93999999999999984</v>
       </c>
@@ -7431,9 +6477,6 @@
       <c r="H247">
         <v>3.2868717804888088E-3</v>
       </c>
-      <c r="I247">
-        <v>0.1327424379484903</v>
-      </c>
       <c r="J247">
         <v>-0.86523809523809503</v>
       </c>
@@ -7463,9 +6506,6 @@
       <c r="H248">
         <v>3.660890077940238E-3</v>
       </c>
-      <c r="I248">
-        <v>5.3776396780803808E-2</v>
-      </c>
       <c r="J248">
         <v>-0.66</v>
       </c>
@@ -7495,9 +6535,6 @@
       <c r="H249">
         <v>8.3907004894285819E-3</v>
       </c>
-      <c r="I249">
-        <v>0.12992542248210889</v>
-      </c>
       <c r="J249">
         <v>-0.69380952380952399</v>
       </c>
@@ -7527,9 +6564,6 @@
       <c r="H250">
         <v>-8.1313615676670281E-4</v>
       </c>
-      <c r="I250">
-        <v>0.19753097545748369</v>
-      </c>
       <c r="J250">
         <v>-0.95043478260869574</v>
       </c>
@@ -7559,9 +6593,6 @@
       <c r="H251">
         <v>-4.6980832483765056E-3</v>
       </c>
-      <c r="I251">
-        <v>7.2759354282428301E-2</v>
-      </c>
       <c r="J251">
         <v>-1.51</v>
       </c>
@@ -7591,9 +6622,6 @@
       <c r="H252">
         <v>3.7901685163870269E-3</v>
       </c>
-      <c r="I252">
-        <v>1.739174271186927E-2</v>
-      </c>
       <c r="J252">
         <v>-2.145</v>
       </c>
@@ -7623,9 +6651,6 @@
       <c r="H253">
         <v>-2.7673215792844991E-4</v>
       </c>
-      <c r="I253">
-        <v>6.6691374498672129E-2</v>
-      </c>
       <c r="J253">
         <v>-1.7373684210526319</v>
       </c>
@@ -7655,9 +6680,6 @@
       <c r="H254">
         <v>9.7162731397304469E-4</v>
       </c>
-      <c r="I254">
-        <v>4.7252884850545573E-2</v>
-      </c>
       <c r="J254">
         <v>-1.5965</v>
       </c>
@@ -7687,9 +6709,6 @@
       <c r="H255">
         <v>5.2578163124135102E-3</v>
       </c>
-      <c r="I255">
-        <v>0</v>
-      </c>
       <c r="J255">
         <v>-1.2549999999999999</v>
       </c>
@@ -7719,9 +6738,6 @@
       <c r="H256">
         <v>6.7725447466671085E-4</v>
       </c>
-      <c r="I256">
-        <v>0.1296778233085325</v>
-      </c>
       <c r="J256">
         <v>-1.507368421052631</v>
       </c>
@@ -7751,9 +6767,6 @@
       <c r="H257">
         <v>1.6692023728239751E-3</v>
       </c>
-      <c r="I257">
-        <v>2.6668247082161312E-2</v>
-      </c>
       <c r="J257">
         <v>-3.0685714285714289</v>
       </c>
@@ -7783,9 +6796,6 @@
       <c r="H258">
         <v>6.7987749316937851E-3</v>
       </c>
-      <c r="I258">
-        <v>3.8714512180690441E-2</v>
-      </c>
       <c r="J258">
         <v>-1.8257142857142861</v>
       </c>
@@ -7815,9 +6825,6 @@
       <c r="H259">
         <v>-4.0220048895633909E-4</v>
       </c>
-      <c r="I259">
-        <v>0</v>
-      </c>
       <c r="J259">
         <v>0.79190476190476222</v>
       </c>
@@ -7847,9 +6854,6 @@
       <c r="H260">
         <v>-2.588003876962119E-3</v>
       </c>
-      <c r="I260">
-        <v>0</v>
-      </c>
       <c r="J260">
         <v>1.621904761904762</v>
       </c>
@@ -7879,9 +6883,6 @@
       <c r="H261">
         <v>-1.247720941467634E-3</v>
       </c>
-      <c r="I261">
-        <v>0</v>
-      </c>
       <c r="J261">
         <v>1.6009090909090911</v>
       </c>
@@ -7911,9 +6912,6 @@
       <c r="H262">
         <v>-3.623053932939158E-3</v>
       </c>
-      <c r="I262">
-        <v>-3.8714512180690441E-2</v>
-      </c>
       <c r="J262">
         <v>0.85952380952380969</v>
       </c>
@@ -7943,9 +6941,6 @@
       <c r="H263">
         <v>-2.1187737976617882E-3</v>
       </c>
-      <c r="I263">
-        <v>-5.4067221270275738E-2</v>
-      </c>
       <c r="J263">
         <v>-1.285714285714267E-2</v>
       </c>
@@ -7975,9 +6970,6 @@
       <c r="H264">
         <v>-1.5253638397965119E-3</v>
       </c>
-      <c r="I264">
-        <v>0</v>
-      </c>
       <c r="J264">
         <v>-0.73909090909090902</v>
       </c>
@@ -8007,9 +6999,6 @@
       <c r="H265">
         <v>-8.9869356360949837E-4</v>
       </c>
-      <c r="I265">
-        <v>0</v>
-      </c>
       <c r="J265">
         <v>-1.4658823529411771</v>
       </c>
@@ -8039,9 +7028,6 @@
       <c r="H266">
         <v>1.2500383081519571E-3</v>
       </c>
-      <c r="I266">
-        <v>2.739897418811443E-2</v>
-      </c>
       <c r="J266">
         <v>-2.0368181818181821</v>
       </c>
@@ -8071,9 +7057,6 @@
       <c r="H267">
         <v>4.1896645366659158E-3</v>
       </c>
-      <c r="I267">
-        <v>2.6668247082161312E-2</v>
-      </c>
       <c r="J267">
         <v>-1.5161904761904761</v>
       </c>
@@ -8103,9 +7086,6 @@
       <c r="H268">
         <v>4.6738731885280771E-3</v>
       </c>
-      <c r="I268">
-        <v>0</v>
-      </c>
       <c r="J268">
         <v>-1.3738888888888889</v>
       </c>
@@ -8135,9 +7115,6 @@
       <c r="H269">
         <v>1.542682772338821E-3</v>
       </c>
-      <c r="I269">
-        <v>0</v>
-      </c>
       <c r="J269">
         <v>-0.5950000000000002</v>
       </c>
@@ -8167,9 +7144,6 @@
       <c r="H270">
         <v>-2.861273919558371E-3</v>
       </c>
-      <c r="I270">
-        <v>0</v>
-      </c>
       <c r="J270">
         <v>-0.64238095238095239</v>
       </c>
@@ -8199,9 +7173,6 @@
       <c r="H271">
         <v>2.3681874623449062E-3</v>
       </c>
-      <c r="I271">
-        <v>0</v>
-      </c>
       <c r="J271">
         <v>-2.097</v>
       </c>
@@ -8231,9 +7202,6 @@
       <c r="H272">
         <v>2.8790496024146961E-3</v>
       </c>
-      <c r="I272">
-        <v>-5.4067221270275738E-2</v>
-      </c>
       <c r="J272">
         <v>-1.3868181818181819</v>
       </c>
@@ -8263,9 +7231,6 @@
       <c r="H273">
         <v>4.2153680531455961E-3</v>
       </c>
-      <c r="I273">
-        <v>0</v>
-      </c>
       <c r="J273">
         <v>-1.437727272727273</v>
       </c>
@@ -8295,9 +7260,6 @@
       <c r="H274">
         <v>1.230763922521305E-3</v>
       </c>
-      <c r="I274">
-        <v>0</v>
-      </c>
       <c r="J274">
         <v>-1.781428571428572</v>
       </c>
@@ -8327,9 +7289,6 @@
       <c r="H275">
         <v>3.6047684811180152E-3</v>
       </c>
-      <c r="I275">
-        <v>0</v>
-      </c>
       <c r="J275">
         <v>-1.1990476190476189</v>
       </c>
@@ -8359,9 +7318,6 @@
       <c r="H276">
         <v>-5.5256281399351792E-6</v>
       </c>
-      <c r="I276">
-        <v>-2.8170876966696401E-2</v>
-      </c>
       <c r="J276">
         <v>-0.2333333333333332</v>
       </c>
@@ -8391,9 +7347,6 @@
       <c r="H277">
         <v>6.5528933445175852E-3</v>
       </c>
-      <c r="I277">
-        <v>2.8170876966696401E-2</v>
-      </c>
       <c r="J277">
         <v>0.98444444444444434</v>
       </c>
@@ -8422,9 +7375,6 @@
       </c>
       <c r="H278">
         <v>-4.0308573162004544E-3</v>
-      </c>
-      <c r="I278">
-        <v>-2.8170876966696401E-2</v>
       </c>
       <c r="J278">
         <v>0.87454545454545451</v>
